--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:55:04-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1282,7 +1282,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
@@ -2368,17 +2368,17 @@
   <dimension ref="A1:AP87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.60546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.57421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.49609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2387,28 +2387,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.8046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.92578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.22265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.8671875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="239.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.87890625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8336,7 +8336,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-10T12:52:28-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:52:28-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T21:50:44-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:50:44-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-18T15:36:33-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1164,7 +1164,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1187,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1539,7 +1539,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1571,7 +1571,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1627,7 +1627,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1660,7 +1660,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1672,7 +1672,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1700,7 +1700,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1780,7 +1780,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1830,7 +1830,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1863,7 +1863,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1900,7 +1900,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1922,7 +1922,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:36:33-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
+++ b/build/output/StructureDefinition-cibmtr-vital-signs-height.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1164,7 +1164,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1187,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1539,7 +1539,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1571,7 +1571,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1627,7 +1627,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1660,7 +1660,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1672,7 +1672,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1700,7 +1700,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1780,7 +1780,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1830,7 +1830,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1863,7 +1863,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1900,7 +1900,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1922,7 +1922,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
